--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.1003848826193</v>
+        <v>8.791312543425637</v>
       </c>
       <c r="D2" t="n">
-        <v>51.56724224720475</v>
+        <v>8.379676865170772</v>
       </c>
       <c r="E2" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F2" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.09718511742216</v>
+        <v>6.353292581581102</v>
       </c>
       <c r="D3" t="n">
-        <v>38.95153386989997</v>
+        <v>6.329624253858745</v>
       </c>
       <c r="E3" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F3" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.63962576914</v>
+        <v>9.528939187485252</v>
       </c>
       <c r="D4" t="n">
-        <v>23.40465290872261</v>
+        <v>3.803256097667424</v>
       </c>
       <c r="E4" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F4" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.95204820181242</v>
+        <v>5.029707832794518</v>
       </c>
       <c r="D5" t="n">
-        <v>30.80233940667549</v>
+        <v>5.005380153584768</v>
       </c>
       <c r="E5" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F5" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.42773433547729</v>
+        <v>5.59450682951506</v>
       </c>
       <c r="D6" t="n">
-        <v>34.30545128496556</v>
+        <v>5.574635833806903</v>
       </c>
       <c r="E6" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F6" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.04773219143847</v>
+        <v>4.070256481108751</v>
       </c>
       <c r="D7" t="n">
-        <v>24.89502832371708</v>
+        <v>4.045442102604025</v>
       </c>
       <c r="E7" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F7" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.02710484769853</v>
+        <v>7.641904537751012</v>
       </c>
       <c r="D8" t="n">
-        <v>20.01110802640485</v>
+        <v>3.251805054290788</v>
       </c>
       <c r="E8" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F8" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.18456575146031</v>
+        <v>4.2549919346123</v>
       </c>
       <c r="D9" t="n">
-        <v>26.09944253509436</v>
+        <v>4.241159411952833</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F9" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.23305400396357</v>
+        <v>5.40037127564408</v>
       </c>
       <c r="D10" t="n">
-        <v>27.40640638812595</v>
+        <v>4.453541038070468</v>
       </c>
       <c r="E10" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F10" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.85979312533506</v>
+        <v>6.639716382866947</v>
       </c>
       <c r="D11" t="n">
-        <v>23.84177941044711</v>
+        <v>3.874289154197655</v>
       </c>
       <c r="E11" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F11" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.33983086912459</v>
+        <v>3.467722516232747</v>
       </c>
       <c r="D12" t="n">
-        <v>21.37941042944148</v>
+        <v>3.47415419478424</v>
       </c>
       <c r="E12" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F12" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.31387348787116</v>
+        <v>5.901004441779064</v>
       </c>
       <c r="D13" t="n">
-        <v>5.077926964316929</v>
+        <v>0.825163131701501</v>
       </c>
       <c r="E13" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F13" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.22299056417108</v>
+        <v>6.698735966677801</v>
       </c>
       <c r="D14" t="n">
-        <v>41.26684278617176</v>
+        <v>6.705861952752912</v>
       </c>
       <c r="E14" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F14" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.72655399655383</v>
+        <v>4.343065024439998</v>
       </c>
       <c r="D15" t="n">
-        <v>25.32052812811967</v>
+        <v>4.114585820819446</v>
       </c>
       <c r="E15" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F15" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.08635203405456</v>
+        <v>4.076532205533866</v>
       </c>
       <c r="D16" t="n">
-        <v>25.20599283632571</v>
+        <v>4.095973835902928</v>
       </c>
       <c r="E16" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F16" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.96741645419549</v>
+        <v>3.407205173806767</v>
       </c>
       <c r="D17" t="n">
-        <v>21.11676906503311</v>
+        <v>3.431474973067881</v>
       </c>
       <c r="E17" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F17" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.79028244522937</v>
+        <v>5.003420897349773</v>
       </c>
       <c r="D18" t="n">
-        <v>29.1351427039057</v>
+        <v>4.734460689384677</v>
       </c>
       <c r="E18" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F18" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.52571424321192</v>
+        <v>6.747928564521938</v>
       </c>
       <c r="D19" t="n">
-        <v>41.6276464117477</v>
+        <v>6.764492541909001</v>
       </c>
       <c r="E19" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F19" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>34.29236601167848</v>
+        <v>5.572509476897753</v>
       </c>
       <c r="D20" t="n">
-        <v>34.44633064046369</v>
+        <v>5.597528729075349</v>
       </c>
       <c r="E20" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F20" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.37569935654094</v>
+        <v>3.473551145437903</v>
       </c>
       <c r="D21" t="n">
-        <v>19.71028050994738</v>
+        <v>3.20292058286645</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F21" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>45.85743489445532</v>
+        <v>7.451833170348989</v>
       </c>
       <c r="D22" t="n">
-        <v>45.98555000653399</v>
+        <v>7.472651876061774</v>
       </c>
       <c r="E22" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F22" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>16.27623249471003</v>
+        <v>2.644887780390379</v>
       </c>
       <c r="D23" t="n">
-        <v>15.43225369730418</v>
+        <v>2.507741225811929</v>
       </c>
       <c r="E23" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F23" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>80.66307603367352</v>
+        <v>13.10774985547195</v>
       </c>
       <c r="D24" t="n">
-        <v>80.75102126317093</v>
+        <v>13.12204095526528</v>
       </c>
       <c r="E24" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F24" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>27.16964015319023</v>
+        <v>4.415066524893413</v>
       </c>
       <c r="D25" t="n">
-        <v>28.82244965430974</v>
+        <v>4.683648068825332</v>
       </c>
       <c r="E25" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F25" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>38.51762199672522</v>
+        <v>6.259113574467849</v>
       </c>
       <c r="D26" t="n">
-        <v>38.51876451214564</v>
+        <v>6.259299233223667</v>
       </c>
       <c r="E26" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F26" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>32.6125898198715</v>
+        <v>5.299545845729119</v>
       </c>
       <c r="D27" t="n">
-        <v>33.21595098981987</v>
+        <v>5.397592035845729</v>
       </c>
       <c r="E27" t="n">
-        <v>13.54516545339691</v>
+        <v>2.201089386176997</v>
       </c>
       <c r="F27" t="n">
-        <v>14.00321044390909</v>
+        <v>2.275521697135228</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
